--- a/backend/data/financials_by_company/0026.HK.xlsx
+++ b/backend/data/financials_by_company/0026.HK.xlsx
@@ -657,570 +657,570 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-211530</v>
+        <v>670725</v>
       </c>
       <c r="C2" t="n">
         <v>0.165</v>
       </c>
       <c r="D2" t="n">
-        <v>34823000</v>
+        <v>42617000</v>
       </c>
       <c r="E2" t="n">
-        <v>-1282000</v>
+        <v>4065000</v>
       </c>
       <c r="F2" t="n">
-        <v>-1282000</v>
+        <v>4065000</v>
       </c>
       <c r="G2" t="n">
-        <v>-262219000</v>
+        <v>-17922000</v>
       </c>
       <c r="H2" t="n">
-        <v>3364000</v>
+        <v>3408000</v>
       </c>
       <c r="I2" t="n">
-        <v>7306000</v>
+        <v>6002000</v>
       </c>
       <c r="J2" t="n">
-        <v>33541000</v>
+        <v>46682000</v>
       </c>
       <c r="K2" t="n">
-        <v>30177000</v>
+        <v>43274000</v>
       </c>
       <c r="L2" t="n">
-        <v>66351000</v>
+        <v>10720000</v>
       </c>
       <c r="M2" t="n">
-        <v>66351000</v>
+        <v>10720000</v>
       </c>
       <c r="N2" t="n">
-        <v>-261148530</v>
+        <v>-21316275</v>
       </c>
       <c r="O2" t="n">
-        <v>-262219000</v>
+        <v>-17922000</v>
       </c>
       <c r="P2" t="n">
-        <v>39373000</v>
+        <v>35108000</v>
       </c>
       <c r="Q2" t="n">
-        <v>413000</v>
+        <v>401000</v>
       </c>
       <c r="R2" t="n">
-        <v>94839000</v>
+        <v>95291000</v>
       </c>
       <c r="S2" t="n">
-        <v>45276856</v>
+        <v>45308056</v>
       </c>
       <c r="T2" t="n">
-        <v>45276856</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+        <v>45308056</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-0.4</v>
+      </c>
       <c r="W2" t="n">
-        <v>-262219000</v>
+        <v>-17922000</v>
       </c>
       <c r="X2" t="n">
-        <v>-262219000</v>
+        <v>-17922000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-262219000</v>
+        <v>-17922000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-262219000</v>
+        <v>-17922000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-262219000</v>
+        <v>-17922000</v>
       </c>
       <c r="AC2" t="n">
-        <v>6706000</v>
+        <v>14776000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-255513000</v>
+        <v>-3146000</v>
       </c>
       <c r="AE2" t="n">
-        <v>525000</v>
+        <v>1420000</v>
       </c>
       <c r="AF2" t="n">
-        <v>537000</v>
+        <v>440000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-537000</v>
+        <v>-440000</v>
       </c>
       <c r="AH2" t="n">
-        <v>66351000</v>
+        <v>10720000</v>
       </c>
       <c r="AI2" t="n">
-        <v>66351000</v>
+        <v>10720000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>30177000</v>
+        <v>43274000</v>
       </c>
       <c r="AK2" t="n">
-        <v>32067000</v>
+        <v>29106000</v>
       </c>
       <c r="AL2" t="n">
-        <v>2989000</v>
+        <v>2232000</v>
       </c>
       <c r="AM2" t="n">
-        <v>3364000</v>
+        <v>3408000</v>
       </c>
       <c r="AN2" t="n">
-        <v>3364000</v>
+        <v>3408000</v>
       </c>
       <c r="AO2" t="n">
-        <v>9517000</v>
+        <v>11006000</v>
       </c>
       <c r="AP2" t="n">
-        <v>9517000</v>
+        <v>11006000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>413000</v>
+        <v>401000</v>
       </c>
       <c r="AR2" t="n">
-        <v>62244000</v>
+        <v>72380000</v>
       </c>
       <c r="AS2" t="n">
-        <v>7306000</v>
+        <v>6002000</v>
       </c>
       <c r="AT2" t="n">
-        <v>69550000</v>
+        <v>78382000</v>
       </c>
       <c r="AU2" t="n">
-        <v>69550000</v>
+        <v>78382000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>-132495</v>
+        <v>-165511.862666</v>
       </c>
       <c r="C3" t="n">
-        <v>0.165</v>
+        <v>0.155703</v>
       </c>
       <c r="D3" t="n">
-        <v>33655000</v>
+        <v>41829000</v>
       </c>
       <c r="E3" t="n">
-        <v>-803000</v>
+        <v>-1063000</v>
       </c>
       <c r="F3" t="n">
-        <v>-803000</v>
+        <v>-1063000</v>
       </c>
       <c r="G3" t="n">
-        <v>-155236000</v>
+        <v>72347000</v>
       </c>
       <c r="H3" t="n">
-        <v>3392000</v>
+        <v>3408000</v>
       </c>
       <c r="I3" t="n">
-        <v>6920000</v>
+        <v>6362000</v>
       </c>
       <c r="J3" t="n">
-        <v>32852000</v>
+        <v>40766000</v>
       </c>
       <c r="K3" t="n">
-        <v>29460000</v>
+        <v>37358000</v>
       </c>
       <c r="L3" t="n">
-        <v>43960000</v>
+        <v>4397000</v>
       </c>
       <c r="M3" t="n">
-        <v>43960000</v>
+        <v>4397000</v>
       </c>
       <c r="N3" t="n">
-        <v>-154565495</v>
+        <v>73244488.137334</v>
       </c>
       <c r="O3" t="n">
-        <v>-155236000</v>
+        <v>72347000</v>
       </c>
       <c r="P3" t="n">
-        <v>37475000</v>
+        <v>35625000</v>
       </c>
       <c r="Q3" t="n">
-        <v>414000</v>
+        <v>385000</v>
       </c>
       <c r="R3" t="n">
-        <v>73853000</v>
+        <v>46678000</v>
       </c>
       <c r="S3" t="n">
-        <v>45298195</v>
+        <v>45308056</v>
       </c>
       <c r="T3" t="n">
-        <v>45298195</v>
+        <v>45308056</v>
       </c>
       <c r="U3" t="n">
-        <v>-3.43</v>
+        <v>1.6</v>
       </c>
       <c r="V3" t="n">
-        <v>-3.43</v>
+        <v>1.6</v>
       </c>
       <c r="W3" t="n">
-        <v>-155236000</v>
+        <v>72347000</v>
       </c>
       <c r="X3" t="n">
-        <v>-155236000</v>
+        <v>72347000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-155236000</v>
+        <v>72347000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-155236000</v>
+        <v>72347000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-155236000</v>
+        <v>72347000</v>
       </c>
       <c r="AC3" t="n">
-        <v>4234000</v>
+        <v>13342000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-151002000</v>
+        <v>85689000</v>
       </c>
       <c r="AE3" t="n">
-        <v>660000</v>
+        <v>486000</v>
       </c>
       <c r="AF3" t="n">
-        <v>462000</v>
+        <v>302000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-462000</v>
+        <v>-302000</v>
       </c>
       <c r="AH3" t="n">
-        <v>43960000</v>
+        <v>4397000</v>
       </c>
       <c r="AI3" t="n">
-        <v>43960000</v>
+        <v>4397000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>29460000</v>
+        <v>37358000</v>
       </c>
       <c r="AK3" t="n">
-        <v>30555000</v>
+        <v>29263000</v>
       </c>
       <c r="AL3" t="n">
-        <v>2906000</v>
+        <v>2579000</v>
       </c>
       <c r="AM3" t="n">
-        <v>3392000</v>
+        <v>3408000</v>
       </c>
       <c r="AN3" t="n">
-        <v>3392000</v>
+        <v>3408000</v>
       </c>
       <c r="AO3" t="n">
-        <v>8775000</v>
+        <v>8850000</v>
       </c>
       <c r="AP3" t="n">
-        <v>8775000</v>
+        <v>8850000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>414000</v>
+        <v>385000</v>
       </c>
       <c r="AR3" t="n">
-        <v>60015000</v>
+        <v>66621000</v>
       </c>
       <c r="AS3" t="n">
-        <v>6920000</v>
+        <v>6362000</v>
       </c>
       <c r="AT3" t="n">
-        <v>66935000</v>
+        <v>72983000</v>
       </c>
       <c r="AU3" t="n">
-        <v>66935000</v>
+        <v>72983000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>-165511.862666</v>
+        <v>-132495</v>
       </c>
       <c r="C4" t="n">
-        <v>0.155703</v>
+        <v>0.165</v>
       </c>
       <c r="D4" t="n">
-        <v>41829000</v>
+        <v>33655000</v>
       </c>
       <c r="E4" t="n">
-        <v>-1063000</v>
+        <v>-803000</v>
       </c>
       <c r="F4" t="n">
-        <v>-1063000</v>
+        <v>-803000</v>
       </c>
       <c r="G4" t="n">
-        <v>72347000</v>
+        <v>-155236000</v>
       </c>
       <c r="H4" t="n">
-        <v>3408000</v>
+        <v>3392000</v>
       </c>
       <c r="I4" t="n">
-        <v>6362000</v>
+        <v>6920000</v>
       </c>
       <c r="J4" t="n">
-        <v>40766000</v>
+        <v>32852000</v>
       </c>
       <c r="K4" t="n">
-        <v>37358000</v>
+        <v>29460000</v>
       </c>
       <c r="L4" t="n">
-        <v>4397000</v>
+        <v>43960000</v>
       </c>
       <c r="M4" t="n">
-        <v>4397000</v>
+        <v>43960000</v>
       </c>
       <c r="N4" t="n">
-        <v>73244488.137334</v>
+        <v>-154565495</v>
       </c>
       <c r="O4" t="n">
-        <v>72347000</v>
+        <v>-155236000</v>
       </c>
       <c r="P4" t="n">
-        <v>35625000</v>
+        <v>37475000</v>
       </c>
       <c r="Q4" t="n">
-        <v>385000</v>
+        <v>414000</v>
       </c>
       <c r="R4" t="n">
-        <v>46678000</v>
+        <v>73853000</v>
       </c>
       <c r="S4" t="n">
-        <v>45308056</v>
+        <v>45298195</v>
       </c>
       <c r="T4" t="n">
-        <v>45308056</v>
+        <v>45298195</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6</v>
+        <v>-3.43</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6</v>
+        <v>-3.43</v>
       </c>
       <c r="W4" t="n">
-        <v>72347000</v>
+        <v>-155236000</v>
       </c>
       <c r="X4" t="n">
-        <v>72347000</v>
+        <v>-155236000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>72347000</v>
+        <v>-155236000</v>
       </c>
       <c r="AA4" t="n">
-        <v>72347000</v>
+        <v>-155236000</v>
       </c>
       <c r="AB4" t="n">
-        <v>72347000</v>
+        <v>-155236000</v>
       </c>
       <c r="AC4" t="n">
-        <v>13342000</v>
+        <v>4234000</v>
       </c>
       <c r="AD4" t="n">
-        <v>85689000</v>
+        <v>-151002000</v>
       </c>
       <c r="AE4" t="n">
-        <v>486000</v>
+        <v>660000</v>
       </c>
       <c r="AF4" t="n">
-        <v>302000</v>
+        <v>462000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-302000</v>
+        <v>-462000</v>
       </c>
       <c r="AH4" t="n">
-        <v>4397000</v>
+        <v>43960000</v>
       </c>
       <c r="AI4" t="n">
-        <v>4397000</v>
+        <v>43960000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>37358000</v>
+        <v>29460000</v>
       </c>
       <c r="AK4" t="n">
-        <v>29263000</v>
+        <v>30555000</v>
       </c>
       <c r="AL4" t="n">
-        <v>2579000</v>
+        <v>2906000</v>
       </c>
       <c r="AM4" t="n">
-        <v>3408000</v>
+        <v>3392000</v>
       </c>
       <c r="AN4" t="n">
-        <v>3408000</v>
+        <v>3392000</v>
       </c>
       <c r="AO4" t="n">
-        <v>8850000</v>
+        <v>8775000</v>
       </c>
       <c r="AP4" t="n">
-        <v>8850000</v>
+        <v>8775000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>385000</v>
+        <v>414000</v>
       </c>
       <c r="AR4" t="n">
-        <v>66621000</v>
+        <v>60015000</v>
       </c>
       <c r="AS4" t="n">
-        <v>6362000</v>
+        <v>6920000</v>
       </c>
       <c r="AT4" t="n">
-        <v>72983000</v>
+        <v>66935000</v>
       </c>
       <c r="AU4" t="n">
-        <v>72983000</v>
+        <v>66935000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>670725</v>
+        <v>-211530</v>
       </c>
       <c r="C5" t="n">
         <v>0.165</v>
       </c>
       <c r="D5" t="n">
-        <v>42617000</v>
+        <v>34823000</v>
       </c>
       <c r="E5" t="n">
-        <v>4065000</v>
+        <v>-1282000</v>
       </c>
       <c r="F5" t="n">
-        <v>4065000</v>
+        <v>-1282000</v>
       </c>
       <c r="G5" t="n">
-        <v>-17922000</v>
+        <v>-262219000</v>
       </c>
       <c r="H5" t="n">
-        <v>3408000</v>
+        <v>3364000</v>
       </c>
       <c r="I5" t="n">
-        <v>6002000</v>
+        <v>7306000</v>
       </c>
       <c r="J5" t="n">
-        <v>46682000</v>
+        <v>33541000</v>
       </c>
       <c r="K5" t="n">
-        <v>43274000</v>
+        <v>30177000</v>
       </c>
       <c r="L5" t="n">
-        <v>10720000</v>
+        <v>66351000</v>
       </c>
       <c r="M5" t="n">
-        <v>10720000</v>
+        <v>66351000</v>
       </c>
       <c r="N5" t="n">
-        <v>-21316275</v>
+        <v>-261148530</v>
       </c>
       <c r="O5" t="n">
-        <v>-17922000</v>
+        <v>-262219000</v>
       </c>
       <c r="P5" t="n">
-        <v>35108000</v>
+        <v>39373000</v>
       </c>
       <c r="Q5" t="n">
-        <v>401000</v>
+        <v>413000</v>
       </c>
       <c r="R5" t="n">
-        <v>95291000</v>
+        <v>94839000</v>
       </c>
       <c r="S5" t="n">
-        <v>45308056</v>
+        <v>45276856</v>
       </c>
       <c r="T5" t="n">
-        <v>45308056</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-0.4</v>
-      </c>
+        <v>45276856</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>-17922000</v>
+        <v>-262219000</v>
       </c>
       <c r="X5" t="n">
-        <v>-17922000</v>
+        <v>-262219000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-17922000</v>
+        <v>-262219000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-17922000</v>
+        <v>-262219000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-17922000</v>
+        <v>-262219000</v>
       </c>
       <c r="AC5" t="n">
-        <v>14776000</v>
+        <v>6706000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-3146000</v>
+        <v>-255513000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1420000</v>
+        <v>525000</v>
       </c>
       <c r="AF5" t="n">
-        <v>440000</v>
+        <v>537000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-440000</v>
+        <v>-537000</v>
       </c>
       <c r="AH5" t="n">
-        <v>10720000</v>
+        <v>66351000</v>
       </c>
       <c r="AI5" t="n">
-        <v>10720000</v>
+        <v>66351000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>43274000</v>
+        <v>30177000</v>
       </c>
       <c r="AK5" t="n">
-        <v>29106000</v>
+        <v>32067000</v>
       </c>
       <c r="AL5" t="n">
-        <v>2232000</v>
+        <v>2989000</v>
       </c>
       <c r="AM5" t="n">
-        <v>3408000</v>
+        <v>3364000</v>
       </c>
       <c r="AN5" t="n">
-        <v>3408000</v>
+        <v>3364000</v>
       </c>
       <c r="AO5" t="n">
-        <v>11006000</v>
+        <v>9517000</v>
       </c>
       <c r="AP5" t="n">
-        <v>11006000</v>
+        <v>9517000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>401000</v>
+        <v>413000</v>
       </c>
       <c r="AR5" t="n">
-        <v>72380000</v>
+        <v>62244000</v>
       </c>
       <c r="AS5" t="n">
-        <v>6002000</v>
+        <v>7306000</v>
       </c>
       <c r="AT5" t="n">
-        <v>78382000</v>
+        <v>69550000</v>
       </c>
       <c r="AU5" t="n">
-        <v>78382000</v>
+        <v>69550000</v>
       </c>
     </row>
   </sheetData>
@@ -1476,44 +1476,40 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>45276856</v>
+        <v>45308056</v>
       </c>
       <c r="C2" t="n">
-        <v>45276856</v>
+        <v>45308056</v>
       </c>
       <c r="D2" t="n">
-        <v>7198532000</v>
+        <v>8083844000</v>
       </c>
       <c r="E2" t="n">
-        <v>7198532000</v>
+        <v>8083844000</v>
       </c>
       <c r="F2" t="n">
-        <v>1346998000</v>
+        <v>2485480000</v>
       </c>
       <c r="G2" t="n">
-        <v>7198532000</v>
+        <v>8083844000</v>
       </c>
       <c r="H2" t="n">
-        <v>7198532000</v>
+        <v>8083844000</v>
       </c>
       <c r="I2" t="n">
-        <v>7198532000</v>
+        <v>8083844000</v>
       </c>
       <c r="J2" t="n">
-        <v>7198532000</v>
+        <v>8083844000</v>
       </c>
       <c r="K2" t="n">
-        <v>7198532000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>5342000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>6836830000</v>
-      </c>
+        <v>8083844000</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
         <v>92537000</v>
       </c>
@@ -1521,136 +1517,142 @@
         <v>92537000</v>
       </c>
       <c r="P2" t="n">
-        <v>99126000</v>
+        <v>96052000</v>
       </c>
       <c r="Q2" t="n">
-        <v>47881000</v>
+        <v>47466000</v>
       </c>
       <c r="R2" t="n">
-        <v>47881000</v>
+        <v>47466000</v>
       </c>
       <c r="S2" t="n">
-        <v>51245000</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
+        <v>48586000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
       <c r="U2" t="n">
-        <v>51245000</v>
+        <v>48586000</v>
       </c>
       <c r="V2" t="n">
-        <v>46817000</v>
+        <v>39217000</v>
       </c>
       <c r="W2" t="n">
-        <v>3978000</v>
+        <v>8750000</v>
       </c>
       <c r="X2" t="n">
-        <v>450000</v>
+        <v>619000</v>
       </c>
       <c r="Y2" t="n">
-        <v>7297658000</v>
+        <v>8179896000</v>
       </c>
       <c r="Z2" t="n">
-        <v>5899415000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+        <v>5645830000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>15983000</v>
+      </c>
       <c r="AB2" t="n">
-        <v>11534000</v>
+        <v>15983000</v>
       </c>
       <c r="AC2" t="n">
-        <v>11534000</v>
+        <v>15983000</v>
       </c>
       <c r="AD2" t="n">
-        <v>3856309000</v>
+        <v>3005258000</v>
       </c>
       <c r="AE2" t="n">
-        <v>2545128000</v>
+        <v>2817277000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1311181000</v>
+        <v>187981000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1941445000</v>
+        <v>2524695000</v>
       </c>
       <c r="AH2" t="n">
-        <v>90127000</v>
+        <v>99894000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-20233000</v>
+        <v>-10069000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>110360000</v>
+        <v>109963000</v>
       </c>
       <c r="AK2" t="n">
         <v>105076000</v>
       </c>
       <c r="AL2" t="n">
-        <v>5284000</v>
+        <v>4887000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1398243000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>2534066000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>3950000</v>
+      </c>
       <c r="AO2" t="n">
-        <v>8747000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>2115000</v>
-      </c>
+        <v>3950000</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>746000</v>
+        <v>579000</v>
       </c>
       <c r="AR2" t="n">
-        <v>1386635000</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>2529537000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>2412418000</v>
+      </c>
       <c r="AT2" t="n">
-        <v>1386635000</v>
+        <v>2529537000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1274405000</v>
+        <v>2412418000</v>
       </c>
       <c r="AV2" t="n">
-        <v>112230000</v>
+        <v>117119000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>45276856</v>
+        <v>45308056</v>
       </c>
       <c r="C3" t="n">
-        <v>45276856</v>
+        <v>45308056</v>
       </c>
       <c r="D3" t="n">
-        <v>7607914000</v>
+        <v>7867159000</v>
       </c>
       <c r="E3" t="n">
-        <v>7607914000</v>
+        <v>7867159000</v>
       </c>
       <c r="F3" t="n">
-        <v>1430321000</v>
+        <v>1452087000</v>
       </c>
       <c r="G3" t="n">
-        <v>7607914000</v>
+        <v>7867159000</v>
       </c>
       <c r="H3" t="n">
-        <v>7607914000</v>
+        <v>7867159000</v>
       </c>
       <c r="I3" t="n">
-        <v>7607914000</v>
+        <v>7867159000</v>
       </c>
       <c r="J3" t="n">
-        <v>7607914000</v>
+        <v>7867159000</v>
       </c>
       <c r="K3" t="n">
-        <v>7607914000</v>
+        <v>7867159000</v>
       </c>
       <c r="L3" t="n">
-        <v>5369000</v>
+        <v>5396000</v>
       </c>
       <c r="M3" t="n">
-        <v>7246185000</v>
+        <v>7505403000</v>
       </c>
       <c r="N3" t="n">
         <v>92537000</v>
@@ -1659,138 +1661,142 @@
         <v>92537000</v>
       </c>
       <c r="P3" t="n">
-        <v>96645000</v>
+        <v>94934000</v>
       </c>
       <c r="Q3" t="n">
-        <v>48852000</v>
+        <v>51232000</v>
       </c>
       <c r="R3" t="n">
-        <v>48852000</v>
+        <v>51232000</v>
       </c>
       <c r="S3" t="n">
-        <v>47793000</v>
+        <v>43702000</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>47793000</v>
+        <v>43702000</v>
       </c>
       <c r="V3" t="n">
-        <v>45170000</v>
+        <v>39337000</v>
       </c>
       <c r="W3" t="n">
-        <v>2342000</v>
+        <v>4133000</v>
       </c>
       <c r="X3" t="n">
-        <v>281000</v>
+        <v>232000</v>
       </c>
       <c r="Y3" t="n">
-        <v>7704559000</v>
+        <v>7962093000</v>
       </c>
       <c r="Z3" t="n">
-        <v>6226445000</v>
+        <v>6466304000</v>
       </c>
       <c r="AA3" t="n">
-        <v>13353000</v>
+        <v>14618000</v>
       </c>
       <c r="AB3" t="n">
-        <v>13353000</v>
+        <v>14618000</v>
       </c>
       <c r="AC3" t="n">
-        <v>13353000</v>
+        <v>14618000</v>
       </c>
       <c r="AD3" t="n">
-        <v>4005144000</v>
+        <v>3990683000</v>
       </c>
       <c r="AE3" t="n">
-        <v>2815195000</v>
+        <v>2855594000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1189949000</v>
+        <v>1135089000</v>
       </c>
       <c r="AG3" t="n">
-        <v>2114611000</v>
+        <v>2364393000</v>
       </c>
       <c r="AH3" t="n">
-        <v>93337000</v>
+        <v>96610000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-16869000</v>
+        <v>-13477000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110206000</v>
+        <v>110087000</v>
       </c>
       <c r="AK3" t="n">
         <v>105076000</v>
       </c>
       <c r="AL3" t="n">
-        <v>5130000</v>
+        <v>5011000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1478114000</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>1495789000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>3351000</v>
+      </c>
       <c r="AO3" t="n">
-        <v>11228000</v>
+        <v>3351000</v>
       </c>
       <c r="AP3" t="n">
-        <v>877000</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>735000</v>
+        <v>487000</v>
       </c>
       <c r="AR3" t="n">
-        <v>1465274000</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+        <v>1491951000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1405278000</v>
+      </c>
       <c r="AT3" t="n">
-        <v>1465274000</v>
+        <v>1491951000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1390371000</v>
+        <v>1405278000</v>
       </c>
       <c r="AV3" t="n">
-        <v>74903000</v>
+        <v>86673000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>45308056</v>
+        <v>45276856</v>
       </c>
       <c r="C4" t="n">
-        <v>45308056</v>
+        <v>45276856</v>
       </c>
       <c r="D4" t="n">
-        <v>7867159000</v>
+        <v>7607914000</v>
       </c>
       <c r="E4" t="n">
-        <v>7867159000</v>
+        <v>7607914000</v>
       </c>
       <c r="F4" t="n">
-        <v>1452087000</v>
+        <v>1430321000</v>
       </c>
       <c r="G4" t="n">
-        <v>7867159000</v>
+        <v>7607914000</v>
       </c>
       <c r="H4" t="n">
-        <v>7867159000</v>
+        <v>7607914000</v>
       </c>
       <c r="I4" t="n">
-        <v>7867159000</v>
+        <v>7607914000</v>
       </c>
       <c r="J4" t="n">
-        <v>7867159000</v>
+        <v>7607914000</v>
       </c>
       <c r="K4" t="n">
-        <v>7867159000</v>
+        <v>7607914000</v>
       </c>
       <c r="L4" t="n">
-        <v>5396000</v>
+        <v>5369000</v>
       </c>
       <c r="M4" t="n">
-        <v>7505403000</v>
+        <v>7246185000</v>
       </c>
       <c r="N4" t="n">
         <v>92537000</v>
@@ -1799,139 +1805,139 @@
         <v>92537000</v>
       </c>
       <c r="P4" t="n">
-        <v>94934000</v>
+        <v>96645000</v>
       </c>
       <c r="Q4" t="n">
-        <v>51232000</v>
+        <v>48852000</v>
       </c>
       <c r="R4" t="n">
-        <v>51232000</v>
+        <v>48852000</v>
       </c>
       <c r="S4" t="n">
-        <v>43702000</v>
+        <v>47793000</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>43702000</v>
+        <v>47793000</v>
       </c>
       <c r="V4" t="n">
-        <v>39337000</v>
+        <v>45170000</v>
       </c>
       <c r="W4" t="n">
-        <v>4133000</v>
+        <v>2342000</v>
       </c>
       <c r="X4" t="n">
-        <v>232000</v>
+        <v>281000</v>
       </c>
       <c r="Y4" t="n">
-        <v>7962093000</v>
+        <v>7704559000</v>
       </c>
       <c r="Z4" t="n">
-        <v>6466304000</v>
+        <v>6226445000</v>
       </c>
       <c r="AA4" t="n">
-        <v>14618000</v>
+        <v>13353000</v>
       </c>
       <c r="AB4" t="n">
-        <v>14618000</v>
+        <v>13353000</v>
       </c>
       <c r="AC4" t="n">
-        <v>14618000</v>
+        <v>13353000</v>
       </c>
       <c r="AD4" t="n">
-        <v>3990683000</v>
+        <v>4005144000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2855594000</v>
+        <v>2815195000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1135089000</v>
+        <v>1189949000</v>
       </c>
       <c r="AG4" t="n">
-        <v>2364393000</v>
+        <v>2114611000</v>
       </c>
       <c r="AH4" t="n">
-        <v>96610000</v>
+        <v>93337000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-13477000</v>
+        <v>-16869000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>110087000</v>
+        <v>110206000</v>
       </c>
       <c r="AK4" t="n">
         <v>105076000</v>
       </c>
       <c r="AL4" t="n">
-        <v>5011000</v>
+        <v>5130000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1495789000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>3351000</v>
-      </c>
+        <v>1478114000</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>3351000</v>
+        <v>11228000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>877000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>487000</v>
+        <v>735000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1491951000</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1405278000</v>
-      </c>
+        <v>1465274000</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>1491951000</v>
+        <v>1465274000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1405278000</v>
+        <v>1390371000</v>
       </c>
       <c r="AV4" t="n">
-        <v>86673000</v>
+        <v>74903000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>45308056</v>
+        <v>45276856</v>
       </c>
       <c r="C5" t="n">
-        <v>45308056</v>
+        <v>45276856</v>
       </c>
       <c r="D5" t="n">
-        <v>8083844000</v>
+        <v>7198532000</v>
       </c>
       <c r="E5" t="n">
-        <v>8083844000</v>
+        <v>7198532000</v>
       </c>
       <c r="F5" t="n">
-        <v>2485480000</v>
+        <v>1346998000</v>
       </c>
       <c r="G5" t="n">
-        <v>8083844000</v>
+        <v>7198532000</v>
       </c>
       <c r="H5" t="n">
-        <v>8083844000</v>
+        <v>7198532000</v>
       </c>
       <c r="I5" t="n">
-        <v>8083844000</v>
+        <v>7198532000</v>
       </c>
       <c r="J5" t="n">
-        <v>8083844000</v>
+        <v>7198532000</v>
       </c>
       <c r="K5" t="n">
-        <v>8083844000</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+        <v>7198532000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5342000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6836830000</v>
+      </c>
       <c r="N5" t="n">
         <v>92537000</v>
       </c>
@@ -1939,101 +1945,95 @@
         <v>92537000</v>
       </c>
       <c r="P5" t="n">
-        <v>96052000</v>
+        <v>99126000</v>
       </c>
       <c r="Q5" t="n">
-        <v>47466000</v>
+        <v>47881000</v>
       </c>
       <c r="R5" t="n">
-        <v>47466000</v>
+        <v>47881000</v>
       </c>
       <c r="S5" t="n">
-        <v>48586000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
+        <v>51245000</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>48586000</v>
+        <v>51245000</v>
       </c>
       <c r="V5" t="n">
-        <v>39217000</v>
+        <v>46817000</v>
       </c>
       <c r="W5" t="n">
-        <v>8750000</v>
+        <v>3978000</v>
       </c>
       <c r="X5" t="n">
-        <v>619000</v>
+        <v>450000</v>
       </c>
       <c r="Y5" t="n">
-        <v>8179896000</v>
+        <v>7297658000</v>
       </c>
       <c r="Z5" t="n">
-        <v>5645830000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>15983000</v>
-      </c>
+        <v>5899415000</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>15983000</v>
+        <v>11534000</v>
       </c>
       <c r="AC5" t="n">
-        <v>15983000</v>
+        <v>11534000</v>
       </c>
       <c r="AD5" t="n">
-        <v>3005258000</v>
+        <v>3856309000</v>
       </c>
       <c r="AE5" t="n">
-        <v>2817277000</v>
+        <v>2545128000</v>
       </c>
       <c r="AF5" t="n">
-        <v>187981000</v>
+        <v>1311181000</v>
       </c>
       <c r="AG5" t="n">
-        <v>2524695000</v>
+        <v>1941445000</v>
       </c>
       <c r="AH5" t="n">
-        <v>99894000</v>
+        <v>90127000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-10069000</v>
+        <v>-20233000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>109963000</v>
+        <v>110360000</v>
       </c>
       <c r="AK5" t="n">
         <v>105076000</v>
       </c>
       <c r="AL5" t="n">
-        <v>4887000</v>
+        <v>5284000</v>
       </c>
       <c r="AM5" t="n">
-        <v>2534066000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>3950000</v>
-      </c>
+        <v>1398243000</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>3950000</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
+        <v>8747000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2115000</v>
+      </c>
       <c r="AQ5" t="n">
-        <v>579000</v>
+        <v>746000</v>
       </c>
       <c r="AR5" t="n">
-        <v>2529537000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2412418000</v>
-      </c>
+        <v>1386635000</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>2529537000</v>
+        <v>1386635000</v>
       </c>
       <c r="AU5" t="n">
-        <v>2412418000</v>
+        <v>1274405000</v>
       </c>
       <c r="AV5" t="n">
-        <v>117119000</v>
+        <v>112230000</v>
       </c>
     </row>
   </sheetData>
@@ -2219,396 +2219,396 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>28976000</v>
-      </c>
-      <c r="C2" t="n">
+        <v>65456000</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>-313000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1121365000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1309255000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>66882000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-254772000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-423693000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-423693000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-423693000</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>103152000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>13711000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>10484000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>79270000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>79270000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-313000</v>
+      </c>
+      <c r="T2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
-        <v>-154000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1211925000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>765157000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-3130000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>449898000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-144613000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-144613000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-144613000</v>
-      </c>
-      <c r="L2" t="n">
+      <c r="U2" t="n">
+        <v>-313000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>65769000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-9968000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-699000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-271000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-1203000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>775000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-10720000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3408000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3408000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-4109000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-7434000</v>
+      </c>
+      <c r="AG2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>565381000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>68793000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>16735000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>525407000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>525407000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-154000</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
-        <v>-154000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>29130000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-7262000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1572000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
-        <v>1566000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-66351000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3364000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3364000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1084000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1884000</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>94839000</v>
+        <v>95291000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>24970000</v>
+        <v>26475000</v>
       </c>
       <c r="C3" t="n">
-        <v>-2348000</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-119000</v>
+        <v>-124000</v>
       </c>
       <c r="E3" t="n">
-        <v>765157000</v>
+        <v>773038000</v>
       </c>
       <c r="F3" t="n">
-        <v>773038000</v>
+        <v>1121365000</v>
       </c>
       <c r="G3" t="n">
-        <v>20247000</v>
+        <v>-56776000</v>
       </c>
       <c r="H3" t="n">
-        <v>-28128000</v>
+        <v>-291551000</v>
       </c>
       <c r="I3" t="n">
-        <v>-141103000</v>
+        <v>-143515000</v>
       </c>
       <c r="J3" t="n">
-        <v>-138755000</v>
+        <v>-143515000</v>
       </c>
       <c r="K3" t="n">
-        <v>-138755000</v>
+        <v>-143515000</v>
       </c>
       <c r="L3" t="n">
-        <v>-2348000</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-2348000</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>87886000</v>
+        <v>-174635000</v>
       </c>
       <c r="O3" t="n">
-        <v>35659000</v>
+        <v>3932000</v>
       </c>
       <c r="P3" t="n">
-        <v>14530000</v>
+        <v>10477000</v>
       </c>
       <c r="Q3" t="n">
-        <v>18796000</v>
+        <v>689259000</v>
       </c>
       <c r="R3" t="n">
-        <v>18796000</v>
+        <v>689259000</v>
       </c>
       <c r="S3" t="n">
-        <v>-119000</v>
+        <v>-124000</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>-119000</v>
+        <v>-124000</v>
       </c>
       <c r="V3" t="n">
-        <v>25089000</v>
+        <v>26599000</v>
       </c>
       <c r="W3" t="n">
-        <v>-9673000</v>
+        <v>-13347000</v>
       </c>
       <c r="X3" t="n">
-        <v>-479000</v>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+        <v>529000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
       <c r="Z3" t="n">
-        <v>-665000</v>
+        <v>-630000</v>
       </c>
       <c r="AA3" t="n">
-        <v>186000</v>
+        <v>1159000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-43960000</v>
+        <v>-4397000</v>
       </c>
       <c r="AC3" t="n">
-        <v>3392000</v>
+        <v>3408000</v>
       </c>
       <c r="AD3" t="n">
-        <v>3392000</v>
+        <v>3408000</v>
       </c>
       <c r="AE3" t="n">
-        <v>735000</v>
+        <v>888000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1221000</v>
+        <v>-7160000</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>73853000</v>
+        <v>46678000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>26475000</v>
+        <v>24970000</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-2348000</v>
       </c>
       <c r="D4" t="n">
-        <v>-124000</v>
+        <v>-119000</v>
       </c>
       <c r="E4" t="n">
+        <v>765157000</v>
+      </c>
+      <c r="F4" t="n">
         <v>773038000</v>
       </c>
-      <c r="F4" t="n">
-        <v>1121365000</v>
-      </c>
       <c r="G4" t="n">
-        <v>-56776000</v>
+        <v>20247000</v>
       </c>
       <c r="H4" t="n">
-        <v>-291551000</v>
+        <v>-28128000</v>
       </c>
       <c r="I4" t="n">
-        <v>-143515000</v>
+        <v>-141103000</v>
       </c>
       <c r="J4" t="n">
-        <v>-143515000</v>
+        <v>-138755000</v>
       </c>
       <c r="K4" t="n">
-        <v>-143515000</v>
+        <v>-138755000</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-2348000</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-2348000</v>
       </c>
       <c r="N4" t="n">
-        <v>-174635000</v>
+        <v>87886000</v>
       </c>
       <c r="O4" t="n">
-        <v>3932000</v>
+        <v>35659000</v>
       </c>
       <c r="P4" t="n">
-        <v>10477000</v>
+        <v>14530000</v>
       </c>
       <c r="Q4" t="n">
-        <v>689259000</v>
+        <v>18796000</v>
       </c>
       <c r="R4" t="n">
-        <v>689259000</v>
+        <v>18796000</v>
       </c>
       <c r="S4" t="n">
-        <v>-124000</v>
+        <v>-119000</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>-124000</v>
+        <v>-119000</v>
       </c>
       <c r="V4" t="n">
-        <v>26599000</v>
+        <v>25089000</v>
       </c>
       <c r="W4" t="n">
-        <v>-13347000</v>
+        <v>-9673000</v>
       </c>
       <c r="X4" t="n">
-        <v>529000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
+        <v>-479000</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>-630000</v>
+        <v>-665000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1159000</v>
+        <v>186000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-4397000</v>
+        <v>-43960000</v>
       </c>
       <c r="AC4" t="n">
-        <v>3408000</v>
+        <v>3392000</v>
       </c>
       <c r="AD4" t="n">
-        <v>3408000</v>
+        <v>3392000</v>
       </c>
       <c r="AE4" t="n">
-        <v>888000</v>
+        <v>735000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-7160000</v>
+        <v>1221000</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>46678000</v>
+        <v>73853000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>65456000</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>28976000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
       <c r="D5" t="n">
-        <v>-313000</v>
+        <v>-154000</v>
       </c>
       <c r="E5" t="n">
-        <v>1121365000</v>
+        <v>1211925000</v>
       </c>
       <c r="F5" t="n">
-        <v>1309255000</v>
+        <v>765157000</v>
       </c>
       <c r="G5" t="n">
-        <v>66882000</v>
+        <v>-3130000</v>
       </c>
       <c r="H5" t="n">
-        <v>-254772000</v>
+        <v>449898000</v>
       </c>
       <c r="I5" t="n">
-        <v>-423693000</v>
+        <v>-144613000</v>
       </c>
       <c r="J5" t="n">
-        <v>-423693000</v>
+        <v>-144613000</v>
       </c>
       <c r="K5" t="n">
-        <v>-423693000</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+        <v>-144613000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
       <c r="N5" t="n">
-        <v>103152000</v>
+        <v>565381000</v>
       </c>
       <c r="O5" t="n">
-        <v>13711000</v>
+        <v>68793000</v>
       </c>
       <c r="P5" t="n">
-        <v>10484000</v>
+        <v>16735000</v>
       </c>
       <c r="Q5" t="n">
-        <v>79270000</v>
+        <v>525407000</v>
       </c>
       <c r="R5" t="n">
-        <v>79270000</v>
+        <v>525407000</v>
       </c>
       <c r="S5" t="n">
-        <v>-313000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
+        <v>-154000</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>-313000</v>
+        <v>-154000</v>
       </c>
       <c r="V5" t="n">
-        <v>65769000</v>
+        <v>29130000</v>
       </c>
       <c r="W5" t="n">
-        <v>-9968000</v>
+        <v>-7262000</v>
       </c>
       <c r="X5" t="n">
-        <v>-699000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-271000</v>
-      </c>
+        <v>1572000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>-1203000</v>
+        <v>1566000</v>
       </c>
       <c r="AA5" t="n">
-        <v>775000</v>
+        <v>6000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-10720000</v>
+        <v>-66351000</v>
       </c>
       <c r="AC5" t="n">
-        <v>3408000</v>
+        <v>3364000</v>
       </c>
       <c r="AD5" t="n">
-        <v>3408000</v>
+        <v>3364000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-4109000</v>
+        <v>1084000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-7434000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
+        <v>1884000</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>95291000</v>
+        <v>94839000</v>
       </c>
     </row>
   </sheetData>
@@ -3148,187 +3148,187 @@
       </c>
       <c r="DA1" t="inlineStr">
         <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -3431,7 +3431,7 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>57.4</v>
+        <v>57.15</v>
       </c>
       <c r="V2" t="n">
         <v>57.2</v>
@@ -3440,10 +3440,10 @@
         <v>57.15</v>
       </c>
       <c r="X2" t="n">
-        <v>58</v>
+        <v>57.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.4</v>
+        <v>57.15</v>
       </c>
       <c r="Z2" t="n">
         <v>57.2</v>
@@ -3452,7 +3452,7 @@
         <v>57.15</v>
       </c>
       <c r="AB2" t="n">
-        <v>58</v>
+        <v>57.4</v>
       </c>
       <c r="AC2" t="n">
         <v>0.6</v>
@@ -3470,28 +3470,28 @@
         <v>0.67</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.285</v>
+        <v>0.277</v>
       </c>
       <c r="AI2" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>4705</v>
+        <v>4258</v>
       </c>
       <c r="AL2" t="n">
-        <v>7543</v>
+        <v>2872</v>
       </c>
       <c r="AM2" t="n">
-        <v>7543</v>
+        <v>2872</v>
       </c>
       <c r="AN2" t="n">
-        <v>57.4</v>
+        <v>56.9</v>
       </c>
       <c r="AO2" t="n">
-        <v>58.5</v>
+        <v>58.55</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
@@ -3503,7 +3503,7 @@
         <v>2595562496</v>
       </c>
       <c r="AS2" t="n">
-        <v>2595562334</v>
+        <v>2584257620</v>
       </c>
       <c r="AT2" t="n">
         <v>52.1</v>
@@ -3521,16 +3521,16 @@
         <v>17.753992</v>
       </c>
       <c r="AY2" t="n">
-        <v>57.608</v>
+        <v>57.826</v>
       </c>
       <c r="AZ2" t="n">
-        <v>58.9895</v>
+        <v>58.7325</v>
       </c>
       <c r="BA2" t="n">
         <v>0.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.008710802</v>
+        <v>0.008748906000000001</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
@@ -3589,10 +3589,10 @@
         <v>11.841</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.06592381</v>
+        <v>0.07830191</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.27697718</v>
+        <v>0.24487448</v>
       </c>
       <c r="BW2" t="n">
         <v>1.1</v>
@@ -3702,140 +3702,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DA2" t="n">
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>4258</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>5.300003</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>0.10172751</v>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>52.1 - 62.0</t>
+        </is>
+      </c>
+      <c r="DF2" t="n">
+        <v>-4.5999985</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>-0.07419352</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>7.8301907</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>1740651475</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>1740651475</v>
+      </c>
+      <c r="DK2" t="b">
         <v>0</v>
       </c>
-      <c r="DB2" t="n">
+      <c r="DL2" t="n">
+        <v>-4.74</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.4259987</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>-0.0073669055</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-1.3324966</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-0.022687552</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>CHINA MOTOR BUS</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>China Motor Bus Company, Limited</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>finmb_2482072</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DZ2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="EB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>0.43744528</v>
+      </c>
+      <c r="EE2" t="n">
         <v>57.4</v>
       </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
+      <c r="EF2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DE2" t="n">
-        <v>1780042104</v>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>finmb_2482072</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DJ2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DL2" t="b">
+      <c r="EG2" t="n">
+        <v>1782109003</v>
+      </c>
+      <c r="EH2" t="b">
         <v>0</v>
       </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>CHINA MOTOR BUS</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>China Motor Bus Company, Limited</t>
-        </is>
-      </c>
-      <c r="DO2" t="n">
-        <v>-4.74</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.20800018</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.0036106128</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-1.5894966</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>-0.026945416</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="n">
+      <c r="EI2" t="n">
         <v>946949400000</v>
       </c>
-      <c r="DY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>57.15 - 58.0</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EB2" t="n">
-        <v>4705</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>5.300003</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0.10172751</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>52.1 - 62.0</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>-4.5999985</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.07419352</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>6.592381</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1740651475</v>
-      </c>
       <c r="EJ2" t="n">
-        <v>1740651475</v>
-      </c>
-      <c r="EK2" t="b">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>57.15 - 57.4</t>
+        </is>
       </c>
       <c r="EL2" t="inlineStr"/>
     </row>
